--- a/CSV/Woodland Mansion.xlsx
+++ b/CSV/Woodland Mansion.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/willem/Documents/GitHub/friend-zone/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/willem/Documents/GitHub/friend-zone/CSV/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11EAFBD5-E30F-0443-820F-01C3A6A99F96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E1FBCEB-17AA-0343-BDC0-4A3AF2D2C1E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19460" yWindow="780" windowWidth="10000" windowHeight="19100" xr2:uid="{EF5563DD-86E3-44AF-B99F-9E11ACF57133}"/>
+    <workbookView xWindow="60" yWindow="9720" windowWidth="11380" windowHeight="9580" xr2:uid="{EF5563DD-86E3-44AF-B99F-9E11ACF57133}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -41,13 +41,13 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
-    <t>nummer</t>
-  </si>
-  <si>
     <t>X</t>
   </si>
   <si>
     <t>Z</t>
+  </si>
+  <si>
+    <t>woodland Mansion</t>
   </si>
 </sst>
 </file>
@@ -426,30 +426,74 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2061EA4-28D3-4349-9580-4EA67BE3ACE4}">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="5.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>-9672</v>
+      </c>
+      <c r="C2">
+        <v>9496</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>-904</v>
+      </c>
+      <c r="C3">
+        <v>-8712</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>-840</v>
+      </c>
+      <c r="C4">
+        <v>9496</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>3256</v>
+      </c>
+      <c r="C5">
+        <v>-9736</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C1" xr:uid="{F2061EA4-28D3-4349-9580-4EA67BE3ACE4}"/>
+  <autoFilter ref="A1:C1" xr:uid="{F2061EA4-28D3-4349-9580-4EA67BE3ACE4}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C7">
+      <sortCondition ref="B1:B7"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
